--- a/testing.xlsx
+++ b/testing.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://salesbridge-my.sharepoint.com/personal/krrish-pawar_bridgestone_co_in/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\Desktop\PROJECTS\Agentic-Ai-Img-Data-Extraction-BSID-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_F25DC773A252ABDACC104885019A5B825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFBE5F44-BECF-4EC0-9BE8-F5D76FC29946}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,46 +24,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Invoice Images</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699213210047648145583250323235.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE0NDI0fGltYWdlL2pwZWd8YURsbUwyaGpPQzh5T1RZNU9ETTRNalUyTVRNeE1DOHhOelk1T1RJeE16SXhNREEwTnpZME9ERTBOVFU0TXpJMU1ETXlNekl6TlM1cWNHY3w2NWFjN2MyNTMwYjkyYWNlY2ViZjcyOWViMTg5NzcyZmUzMzI0ZWU1N2NmZDNmYmE4MmY2NDljMmQ5MjQwOTA5</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699214554206500930782614712393.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE2MjYxfGltYWdlL2pwZWd8YUdOakwyZzVaQzh5T1RZNU9EY3dOamd6TXpRek9DOHhOelk1T1RJeE5EVTFOREl3TmpVd01Ea3pNRGM0TWpZeE5EY3hNak01TXk1cWNHY3w4MDM0MmRkNTRkODBkMDNmOTViOGNkNzllMzE4OWY2NDc5NWI3YTc5YzdjMjVjN2QzYWNiYWFmZjk2MWZkNGE5</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699215674415821011186792273594.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTA4ODg1fGltYWdlL2pwZWd8YUdZMUwyaGxZeTh5T1RZNU9EY3dOekE1TlRVNE1pOHhOelk1T1RJeE5UWTNORFF4TlRneU1UQXhNVEU0TmpjNU1qSTNNelU1TkM1cWNHY3w0ZTEwYzExNGI4YmZjMjRiMWI3ZDFlZTg5NDkwNmZiM2Y5YWE4OWUzODg1MDliYWNkMTE3NDQyZGNlYTNjNTg3</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699216826855792982879120116292.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE0NzAwfGltYWdlL2pwZWd8YURZNEwyaGtaUzh5T1RZNU9ETTRNekE0TlRVNU9DOHhOelk1T1RJeE5qZ3lOamcxTlRjNU1qazRNamczT1RFeU1ERXhOakk1TWk1cWNHY3xjMGU5OTU2OGRhZTQ4M2JhYjlhNDQ0NTg5ZmVhMDRmZTk4NDkxYmZjY2VlNGQzMmZlMGVhOThkM2E4YzQzYjVj</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699223323085622964876873814847.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE0NjcyfGltYWdlL2pwZWd8YURBMEwyZzVNaTh5T1RZNU9EY3dPRGN6TXprNE1pOHhOelk1T1RJeU16TXlNekE0TlRZeU1qazJORGczTmpnM016Z3hORGcwTnk1cWNHY3w5OWYzOWRhZDY2OTQ3YzhmZTY2ZjQ4ZDczNzNiYmQwMWM2NmI2MWM0MDAwNmFjMGFhOTg2NmNkNTBmMzY4Yzhk</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699230510351547410896784056700.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE1NDYzfGltYWdlL2pwZWd8YURnMkwyaGlNQzh5T1RZNU9EY3hNVFE0TmpRNU5DOHhOelk1T1RJek1EVXhNRE0xTVRVME56UXhNRGc1TmpjNE5EQTFOamN3TUM1cWNHY3wwZGY2OWM0MmNiNDIyYTE2MzgxOWU1NDUyM2Y4MjFjMjUwMDUxMGFkODZhZDY2ZGE5NmNiZmNmNDIwNTNmNWIz</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699241347961397978470649130123.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE5ODAzfGltYWdlL2pwZWd8YUdFMkwyaG1PUzh5T1RZNU9EY3hOVFUwT1RjeU5pOHhOelk1T1RJME1UTTBOemsyTVRNNU56azNPRFEzTURZME9URXpNREV5TXk1cWNHY3w1NDFiZDM1OGRjYzA2MWI2ZWMzN2VlZGY1NDAxY2ViNDgwZTUyZjMwZjRmNDBkMWU2NzJlMmFjN2YyOWY3YzY4</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/1769951543947962301694217897150.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTIwODUwfGltYWdlL2pwZWd8YURGbEwyZ3pNUzh5T1RjeU16UTBNREU0TlRNM05DOHhOelk1T1RVeE5UUXpPVFEzT1RZeU16QXhOamswTWpFM09EazNNVFV3TG1wd1p3fGFjOWI5OTExYmVjYjY5Mzk1ZTk2NTY0NTZlOWMwOWZjNzBlY2NmMDkxOWRmODY4M2Y0ZTI3Y2EwNTMwN2RmNjI</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/1769513209269.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE3MTAyfGltYWdlL2pwZWd8YURBNEwyaG1PQzh5T1RjeE9URXpNakkwTVRrMU1DOHhOelk1TlRFek1qQTVNalk1TG1wd1p3fDBlODMyM2MyODczYTM4ZTU4ZmE4OTFjODQzYzdmYjRkZWMzNThmNjA0YjRiNWQ2NjZiMjg0NzYyYWFjZTk5NmY</t>
-  </si>
-  <si>
-    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/Sell-Products-Job-Card-Creation-Autorox.pdf?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8ODQyMDA4fGFwcGxpY2F0aW9uL3BkZnxhRGs1TDJnMU1TOHlPVGM0T0RVM01ESTFOVE01TUM5VFpXeHNJRkJ5YjJSMVkzUnpJRXB2WWlCRFlYSmtJRU55WldGMGFXOXVJQzBnUVhWMGIzSnZlQzV3WkdZfGYzNWEyMDJjMDdkZmQwMzFiZDIwMjg5OGU4ZWQ2ODc2NjUyYWZmODA5YWEzMzI3MmEyZDRjZDYzMTYyOGNiOWY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702719260617164510107539457489.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTEyMjE0fGltYWdlL2pwZWd8YURFMkwyaG1PQzh5T1Rnek5UTXlOalExTlRnek9DOHhOemN3TWpjeE9USTJNRFl4TnpFMk5EVXhNREV3TnpVek9UUTFOelE0T1M1cWNHY3xkYTc0NmVkMzk5Y2ZmZWJmYWUyODc2OGRlNDkwZDY2OTFhMDNlZTI2YzNmOGM1NzIzNTBmYTA1YmU5ZmE2ZTll</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702745230506109391809392747970.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTI0MTUxfGltYWdlL2pwZWd8YURoakwyaGpaUzh5T1Rnek5qUTBNRFUyTnpnek9DOHhOemN3TWpjME5USXpNRFV3TmpFd09UTTVNVGd3T1RNNU1qYzBOemszTUM1cWNHY3w5NzU0NmY0OWI2MzM3MzgxN2M0NDdiM2RkNGNhODRiYzg2NjlhNzY5NDBmNmVmMDFjNTFiMDYyMjljMzA5MDNi</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17701937402518413102739324440654.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTEzNzM2fGltYWdlL2pwZWd8YURCaUwyaGxNaTh5T1Rnd09UQTRNalk1TlRjeE1DOHhOemN3TVRrek56UXdNalV4T0RReE16RXdNamN6T1RNeU5EUTBNRFkxTkM1cWNHY3w4ZThkMGM0ZDA2MjIzNTcxNzk4YzE0YjNjOGE0OTJjZDk5MDYyYTA3MDE3ZTlmYWEyZmQxZjc2ZDBiODIyZjJj</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/image.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTIwNTI0fGltYWdlL2pwZWd8YUdVekwyaGlNUzh5T1RjeE56Y3dNVEU1TnpnMU5DOXBiV0ZuWlM1cWNHY3xjYmRlOWRiNGM0MGE1M2FiOTM3ODRlYmRjZTM4ZDY3ZjgwYTc4NjFkZjEwYzFmZDkyYzEyY2MxYjAwOGJjZGJk</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702764381938396460913947222556.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTEyODAwfGltYWdlL2pwZWd8YURJNUwyZzBZUzh5T1Rnek9ETTBOakl5TXpZME5pOHhOemN3TWpjMk5ETTRNVGt6T0RNNU5qUTJNRGt4TXprME56SXlNalUxTmk1cWNHY3xjNTljNDJjYjlmNzMxMTc1NzY4MjllN2UzZjU2M2RjNjk0ODc5MzIwODJmOGZhOTZkYmQ2MzEzNDFmYzlkYmQx</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17700290073737488283448509556497.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8MjUwMzExfGltYWdlL2pwZWd8YUdRNUwyZzRaUzh5T1RjME16YzNOVFl4TWprMU9DOHhOemN3TURJNU1EQTNNemN6TnpRNE9ESTRNelEwT0RVd09UVTFOalE1Tnk1cWNHY3xlZjI0YzUxNjIyZjY4ZTA1OGIzMGYwNGM2MjNkYjAyYzIxMjM1YjRkNTg0MjBhZDNlNzY1NjE0NmU4ZWQ2OWNl</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/Sales-1932.pdf?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NDQzOTh8YXBwbGljYXRpb24vcGRmfGFETmhMMmhtTXk4eU9UYzROamcyT1RjeU56STJNaTlUWVd4bGMxOHhPVE15TG5Ca1pnfDhhZGYzMzA2NjNkMDZmNTkwMDY1OWY1NjM3NzRkZjViYWVkMWQ4YjdlMmNmNmE3OWQ0NmZlY2YzMjViMjVjOGM</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702694215184615927725562672792.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTA2MTQxfGltYWdlL2pwZWd8YURobUwyaGpZeTh5T1Rnek5USTVPVGszT1RJNU5DOHhOemN3TWpZNU5ESXhOVEU0TkRZeE5Ua3lOemN5TlRVMk1qWTNNamM1TWk1cWNHY3xhYzhkNjg3ZmZiY2Y4MzdmYWU0MzVmNjFhYmFjMjVkYmQyMTc2YjVhMzM4YjA1ZTZlYzIzYWQ0ODA2MTExOTlj</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/1769921879114112577189804627747.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTIwODY1fGltYWdlL2pwZWd8YUdSaUwyaGtNQzh5T1RZNU9ETTRNelEzT0RneE5DOHhOelk1T1RJeE9EYzVNVEUwTVRFeU5UYzNNVGc1T0RBME5qSTNOelEzTG1wd1p3fGE0ZGM3YzI2ZWMxOTE2NjkwMjcyOTI2MWM1YjgyODIzY2RkMjFjYWFmODJhZTZlYWEwNjhjZDBhY2JjOGM4MzA</t>
+  </si>
+  <si>
+    <t>https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17701248644324642553755971901623.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTA2Mjg3fGltYWdlL2pwZWd8YUdZMUwyZzJZaTh5T1RjNE56YzJOalExTmpNMU1DOHhOemN3TVRJME9EWTBORE15TkRZME1qVTFNemMxTlRrM01Ua3dNVFl5TXk1cWNHY3xhYTk4OTMyY2MxNThiZTg1ZmY2ZGU5NjUwZTM3MWM2NGZhNDdlYmNlYmRiODg0YzA5MzRiYTRmNjM4MGRkZTkx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,7 +84,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -99,18 +95,6 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor theme="1" tint="0.249977111117893"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.44999542222357858"/>
-        <bgColor theme="1" tint="0.44999542222357858"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,17 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -441,80 +420,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="97" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1" ht="23.25">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="2" spans="1:1" ht="75">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:1" ht="75">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:1" ht="75">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:1" ht="60">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="1:1" ht="75">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:1" ht="75">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:1" ht="60">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+    <row r="9" spans="1:1" ht="75">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="10" spans="1:1" ht="75">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:1" ht="75">
+      <c r="A11" s="2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699214554206500930782614712393.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE2MjYxfGltYWdlL2pwZWd8YUdOakwyZzVaQzh5T1RZNU9EY3dOamd6TXpRek9DOHhOelk1T1RJeE5EVTFOREl3TmpVd01Ea3pNRGM0TWpZeE5EY3hNak01TXk1cWNHY3w4MDM0MmRkNTRkODBkMDNmOTViOGNkNzllMzE4OWY2NDc5NWI3YTc5YzdjMjVjN2QzYWNiYWFmZjk2MWZkNGE5" xr:uid="{36D1CA69-A34A-46D2-A120-0BC992F29758}"/>
-    <hyperlink ref="A5" r:id="rId2" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699216826855792982879120116292.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE0NzAwfGltYWdlL2pwZWd8YURZNEwyaGtaUzh5T1RZNU9ETTRNekE0TlRVNU9DOHhOelk1T1RJeE5qZ3lOamcxTlRjNU1qazRNamczT1RFeU1ERXhOakk1TWk1cWNHY3xjMGU5OTU2OGRhZTQ4M2JhYjlhNDQ0NTg5ZmVhMDRmZTk4NDkxYmZjY2VlNGQzMmZlMGVhOThkM2E4YzQzYjVj" xr:uid="{932ED806-6492-4649-ABEC-179058A417AE}"/>
-    <hyperlink ref="A2" r:id="rId3" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699213210047648145583250323235.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE0NDI0fGltYWdlL2pwZWd8YURsbUwyaGpPQzh5T1RZNU9ETTRNalUyTVRNeE1DOHhOelk1T1RJeE16SXhNREEwTnpZME9ERTBOVFU0TXpJMU1ETXlNekl6TlM1cWNHY3w2NWFjN2MyNTMwYjkyYWNlY2ViZjcyOWViMTg5NzcyZmUzMzI0ZWU1N2NmZDNmYmE4MmY2NDljMmQ5MjQwOTA5" xr:uid="{B15DCD3F-FA04-48A8-83FA-F2BB12D299D2}"/>
-    <hyperlink ref="A6" r:id="rId4" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699223323085622964876873814847.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE0NjcyfGltYWdlL2pwZWd8YURBMEwyZzVNaTh5T1RZNU9EY3dPRGN6TXprNE1pOHhOelk1T1RJeU16TXlNekE0TlRZeU1qazJORGczTmpnM016Z3hORGcwTnk1cWNHY3w5OWYzOWRhZDY2OTQ3YzhmZTY2ZjQ4ZDczNzNiYmQwMWM2NmI2MWM0MDAwNmFjMGFhOTg2NmNkNTBmMzY4Yzhk" xr:uid="{47666AA0-3512-444C-9B9D-60EC495D1C2B}"/>
-    <hyperlink ref="A4" r:id="rId5" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699215674415821011186792273594.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTA4ODg1fGltYWdlL2pwZWd8YUdZMUwyaGxZeTh5T1RZNU9EY3dOekE1TlRVNE1pOHhOelk1T1RJeE5UWTNORFF4TlRneU1UQXhNVEU0TmpjNU1qSTNNelU1TkM1cWNHY3w0ZTEwYzExNGI4YmZjMjRiMWI3ZDFlZTg5NDkwNmZiM2Y5YWE4OWUzODg1MDliYWNkMTE3NDQyZGNlYTNjNTg3" xr:uid="{6FEECF98-2970-4331-BC27-209D5AB56065}"/>
-    <hyperlink ref="A7" r:id="rId6" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699230510351547410896784056700.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE1NDYzfGltYWdlL2pwZWd8YURnMkwyaGlNQzh5T1RZNU9EY3hNVFE0TmpRNU5DOHhOelk1T1RJek1EVXhNRE0xTVRVME56UXhNRGc1TmpjNE5EQTFOamN3TUM1cWNHY3wwZGY2OWM0MmNiNDIyYTE2MzgxOWU1NDUyM2Y4MjFjMjUwMDUxMGFkODZhZDY2ZGE5NmNiZmNmNDIwNTNmNWIz" xr:uid="{7AB789B7-5DAA-4CD2-A455-97B1B2FD2A3C}"/>
-    <hyperlink ref="A8" r:id="rId7" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17699241347961397978470649130123.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE5ODAzfGltYWdlL2pwZWd8YUdFMkwyaG1PUzh5T1RZNU9EY3hOVFUwT1RjeU5pOHhOelk1T1RJME1UTTBOemsyTVRNNU56azNPRFEzTURZME9URXpNREV5TXk1cWNHY3w1NDFiZDM1OGRjYzA2MWI2ZWMzN2VlZGY1NDAxY2ViNDgwZTUyZjMwZjRmNDBkMWU2NzJlMmFjN2YyOWY3YzY4" xr:uid="{CE5DADFF-EE10-49AC-AC8F-20B0DB60E798}"/>
-    <hyperlink ref="A9" r:id="rId8" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/1769951543947962301694217897150.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTIwODUwfGltYWdlL2pwZWd8YURGbEwyZ3pNUzh5T1RjeU16UTBNREU0TlRNM05DOHhOelk1T1RVeE5UUXpPVFEzT1RZeU16QXhOamswTWpFM09EazNNVFV3TG1wd1p3fGFjOWI5OTExYmVjYjY5Mzk1ZTk2NTY0NTZlOWMwOWZjNzBlY2NmMDkxOWRmODY4M2Y0ZTI3Y2EwNTMwN2RmNjI" xr:uid="{D742ACA9-0749-41B4-BA9C-196C3A53D19F}"/>
-    <hyperlink ref="A10" r:id="rId9" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/1769513209269.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTE3MTAyfGltYWdlL2pwZWd8YURBNEwyaG1PQzh5T1RjeE9URXpNakkwTVRrMU1DOHhOelk1TlRFek1qQTVNalk1TG1wd1p3fDBlODMyM2MyODczYTM4ZTU4ZmE4OTFjODQzYzdmYjRkZWMzNThmNjA0YjRiNWQ2NjZiMjg0NzYyYWFjZTk5NmY" xr:uid="{6D009732-964A-4F91-BC65-92F0D1150137}"/>
-    <hyperlink ref="A11" r:id="rId10" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/Sell-Products-Job-Card-Creation-Autorox.pdf?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8ODQyMDA4fGFwcGxpY2F0aW9uL3BkZnxhRGs1TDJnMU1TOHlPVGM0T0RVM01ESTFOVE01TUM5VFpXeHNJRkJ5YjJSMVkzUnpJRXB2WWlCRFlYSmtJRU55WldGMGFXOXVJQzBnUVhWMGIzSnZlQzV3WkdZfGYzNWEyMDJjMDdkZmQwMzFiZDIwMjg5OGU4ZWQ2ODc2NjUyYWZmODA5YWEzMzI3MmEyZDRjZDYzMTYyOGNiOWY" xr:uid="{ECF40D59-8039-4267-A5D8-E9DF328B3192}"/>
+    <hyperlink ref="A5" r:id="rId1" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/image.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTIwNTI0fGltYWdlL2pwZWd8YUdVekwyaGlNUzh5T1RjeE56Y3dNVEU1TnpnMU5DOXBiV0ZuWlM1cWNHY3xjYmRlOWRiNGM0MGE1M2FiOTM3ODRlYmRjZTM4ZDY3ZjgwYTc4NjFkZjEwYzFmZDkyYzEyY2MxYjAwOGJjZGJk"/>
+    <hyperlink ref="A10" r:id="rId2" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/1769921879114112577189804627747.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTIwODY1fGltYWdlL2pwZWd8YUdSaUwyaGtNQzh5T1RZNU9ETTRNelEzT0RneE5DOHhOelk1T1RJeE9EYzVNVEUwTVRFeU5UYzNNVGc1T0RBME5qSTNOelEzTG1wd1p3fGE0ZGM3YzI2ZWMxOTE2NjkwMjcyOTI2MWM1YjgyODIzY2RkMjFjYWFmODJhZTZlYWEwNjhjZDBhY2JjOGM4MzA"/>
+    <hyperlink ref="A7" r:id="rId3" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17700290073737488283448509556497.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8MjUwMzExfGltYWdlL2pwZWd8YUdRNUwyZzRaUzh5T1RjME16YzNOVFl4TWprMU9DOHhOemN3TURJNU1EQTNNemN6TnpRNE9ESTRNelEwT0RVd09UVTFOalE1Tnk1cWNHY3xlZjI0YzUxNjIyZjY4ZTA1OGIzMGYwNGM2MjNkYjAyYzIxMjM1YjRkNTg0MjBhZDNlNzY1NjE0NmU4ZWQ2OWNl"/>
+    <hyperlink ref="A8" r:id="rId4" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/Sales-1932.pdf?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NDQzOTh8YXBwbGljYXRpb24vcGRmfGFETmhMMmhtTXk4eU9UYzROamcyT1RjeU56STJNaTlUWVd4bGMxOHhPVE15TG5Ca1pnfDhhZGYzMzA2NjNkMDZmNTkwMDY1OWY1NjM3NzRkZjViYWVkMWQ4YjdlMmNmNmE3OWQ0NmZlY2YzMjViMjVjOGM"/>
+    <hyperlink ref="A11" r:id="rId5" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17701248644324642553755971901623.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTA2Mjg3fGltYWdlL2pwZWd8YUdZMUwyZzJZaTh5T1RjNE56YzJOalExTmpNMU1DOHhOemN3TVRJME9EWTBORE15TkRZME1qVTFNemMxTlRrM01Ua3dNVFl5TXk1cWNHY3xhYTk4OTMyY2MxNThiZTg1ZmY2ZGU5NjUwZTM3MWM2NGZhNDdlYmNlYmRiODg0YzA5MzRiYTRmNjM4MGRkZTkx"/>
+    <hyperlink ref="A4" r:id="rId6" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17701937402518413102739324440654.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTEzNzM2fGltYWdlL2pwZWd8YURCaUwyaGxNaTh5T1Rnd09UQTRNalk1TlRjeE1DOHhOemN3TVRrek56UXdNalV4T0RReE16RXdNamN6T1RNeU5EUTBNRFkxTkM1cWNHY3w4ZThkMGM0ZDA2MjIzNTcxNzk4YzE0YjNjOGE0OTJjZDk5MDYyYTA3MDE3ZTlmYWEyZmQxZjc2ZDBiODIyZjJj"/>
+    <hyperlink ref="A9" r:id="rId7" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702694215184615927725562672792.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTA2MTQxfGltYWdlL2pwZWd8YURobUwyaGpZeTh5T1Rnek5USTVPVGszT1RJNU5DOHhOemN3TWpZNU5ESXhOVEU0TkRZeE5Ua3lOemN5TlRVMk1qWTNNamM1TWk1cWNHY3xhYzhkNjg3ZmZiY2Y4MzdmYWU0MzVmNjFhYmFjMjVkYmQyMTc2YjVhMzM4YjA1ZTZlYzIzYWQ0ODA2MTExOTlj"/>
+    <hyperlink ref="A2" r:id="rId8" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702719260617164510107539457489.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTEyMjE0fGltYWdlL2pwZWd8YURFMkwyaG1PQzh5T1Rnek5UTXlOalExTlRnek9DOHhOemN3TWpjeE9USTJNRFl4TnpFMk5EVXhNREV3TnpVek9UUTFOelE0T1M1cWNHY3xkYTc0NmVkMzk5Y2ZmZWJmYWUyODc2OGRlNDkwZDY2OTFhMDNlZTI2YzNmOGM1NzIzNTBmYTA1YmU5ZmE2ZTll"/>
+    <hyperlink ref="A3" r:id="rId9" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702745230506109391809392747970.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTI0MTUxfGltYWdlL2pwZWd8YURoakwyaGpaUzh5T1Rnek5qUTBNRFUyTnpnek9DOHhOemN3TWpjME5USXpNRFV3TmpFd09UTTVNVGd3T1RNNU1qYzBOemszTUM1cWNHY3w5NzU0NmY0OWI2MzM3MzgxN2M0NDdiM2RkNGNhODRiYzg2NjlhNzY5NDBmNmVmMDFjNTFiMDYyMjljMzA5MDNi"/>
+    <hyperlink ref="A6" r:id="rId10" display="https://api.cuup0dd28g-bridgesto1-p1-public.model-t.cc.commerce.ondemand.com/medias/17702764381938396460913947222556.jpg?context=bWFzdGVyfFdhcnJhbnR5X0ludm9pY2V8NTEyODAwfGltYWdlL2pwZWd8YURJNUwyZzBZUzh5T1Rnek9ETTBOakl5TXpZME5pOHhOemN3TWpjMk5ETTRNVGt6T0RNNU5qUTJNRGt4TXprME56SXlNalUxTmk1cWNHY3xjNTljNDJjYjlmNzMxMTc1NzY4MjllN2UzZjU2M2RjNjk0ODc5MzIwODJmOGZhOTZkYmQ2MzEzNDFmYzlkYmQx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
